--- a/public/data/software_catalog.xlsx
+++ b/public/data/software_catalog.xlsx
@@ -399,6 +399,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L36"/>
+  <cols>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="44.83203125" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="33.83203125" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="80.83203125" customWidth="1"/>
+    <col min="10" max="10" width="55.83203125" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1778,6 +1792,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="79.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
